--- a/SprintWorkspace/Magicbricks/src/test/resources/ExcelData/Data.xlsx
+++ b/SprintWorkspace/Magicbricks/src/test/resources/ExcelData/Data.xlsx
@@ -8,17 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Windows\System32\config\systemprofile\SprintWorkspace\Magicbricks\src\test\resources\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF47A87F-E806-4F5D-AE48-222E08BDD45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975C5561-31A1-4221-AA2A-958D31658E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1780" yWindow="1780" windowWidth="14400" windowHeight="8170" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="InvestmentHotspot" sheetId="1" r:id="rId1"/>
-    <sheet name="CityData" sheetId="3" r:id="rId2"/>
-    <sheet name="InvalidInvestmentHotspot" sheetId="2" r:id="rId3"/>
+    <sheet name="InvalidInvestmentHotspot" sheetId="2" r:id="rId2"/>
+    <sheet name="CityData" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -440,26 +439,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A68F158-084D-4EDF-9503-AFB1C3D686D6}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{529A163B-E132-417C-8015-8BC166AE93BD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -480,6 +459,9 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>0</v>
+      </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
@@ -504,4 +486,24 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A68F158-084D-4EDF-9503-AFB1C3D686D6}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>